--- a/Моделирование и средства проетирования информационных систем и технологий/Лаб 9-10.xlsx
+++ b/Моделирование и средства проетирования информационных систем и технологий/Лаб 9-10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My\data-storage\Моделирование и средства проетирования информационных систем и технологий\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8604CA3-D2C0-4FE0-B5EF-C2A35951093A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8167BC8-29FF-49F9-8AF4-F3CDDE0FF738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="360" windowWidth="29040" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="56">
   <si>
     <t>Исполнители и выполняемые стадии / работы</t>
   </si>
@@ -90,24 +90,9 @@
     <t>Коп (маш. вр.)</t>
   </si>
   <si>
-    <t>Аналитик (бизнес-анализ)</t>
-  </si>
-  <si>
-    <t>1. Анализ кредитного процесса (документооборот, скоринг, проверки)</t>
-  </si>
-  <si>
-    <t>2. Формализация требований к ИС (ТЗ, прототипы экранов)</t>
-  </si>
-  <si>
     <t>Руководитель проекта</t>
   </si>
   <si>
-    <t>3. Управление проектом, согласование, постановка задач</t>
-  </si>
-  <si>
-    <t>Программист (разработка и отладка)</t>
-  </si>
-  <si>
     <t>4. Разработка модуля «Анкета заемщика и скоринг»</t>
   </si>
   <si>
@@ -120,9 +105,6 @@
     <t>7. Тестирование и отладка</t>
   </si>
   <si>
-    <t>ИТОГО по стадиям</t>
-  </si>
-  <si>
     <t>Исполнители и подпроцессы</t>
   </si>
   <si>
@@ -229,13 +211,43 @@
   </si>
   <si>
     <t>затраты на внедрение??</t>
+  </si>
+  <si>
+    <t>Аналитик</t>
+  </si>
+  <si>
+    <t>Программист</t>
+  </si>
+  <si>
+    <t>Инженер</t>
+  </si>
+  <si>
+    <t>8. Внедрение системы, настройка, обучение персонала</t>
+  </si>
+  <si>
+    <t>2. Анализ кредитного процесса (документооборот, скоринг, проверки)</t>
+  </si>
+  <si>
+    <t>3. Формализация требований к ИС (ТЗ, прототипы экранов)</t>
+  </si>
+  <si>
+    <t>1. Управление проектом, согласование, постановка задач</t>
+  </si>
+  <si>
+    <t>З/п</t>
+  </si>
+  <si>
+    <t>ИТОГО</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
+  </numFmts>
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -279,8 +291,24 @@
       <name val="Tahoma"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -289,14 +317,44 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top/>
       <bottom/>
@@ -306,7 +364,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -317,17 +375,66 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -613,7 +720,7 @@
   <sheetFormatPr defaultRowHeight="43.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" style="8" customWidth="1"/>
     <col min="3" max="3" width="27.7109375" customWidth="1"/>
     <col min="4" max="4" width="21.85546875" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
@@ -628,304 +735,389 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="E1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3">
-        <v>500</v>
-      </c>
-      <c r="D2" s="3">
-        <v>650</v>
-      </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="B2" s="20">
+        <v>200000</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12">
+        <f>B2/160</f>
+        <v>1250</v>
+      </c>
+      <c r="E2" s="12">
+        <f>D2*1.3</f>
+        <v>1625</v>
+      </c>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12">
+        <v>6.28</v>
+      </c>
+      <c r="H2" s="10"/>
       <c r="I2" s="3"/>
     </row>
     <row r="3" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1">
+        <v>53</v>
+      </c>
+      <c r="B3" s="19"/>
+      <c r="C3" s="5">
+        <v>15</v>
+      </c>
+      <c r="D3" s="9">
+        <f>D2*C3</f>
+        <v>18750</v>
+      </c>
+      <c r="E3" s="17">
+        <f t="shared" ref="E3:E13" si="0">D3*1.3</f>
+        <v>24375</v>
+      </c>
+      <c r="F3" s="5">
+        <v>15</v>
+      </c>
+      <c r="H3" s="9">
+        <f>F3*$G$2</f>
+        <v>94.2</v>
+      </c>
+      <c r="I3" s="3"/>
+    </row>
+    <row r="4" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="21">
+        <v>100000</v>
+      </c>
+      <c r="C4" s="22"/>
+      <c r="D4" s="12">
+        <f>B4/160</f>
+        <v>625</v>
+      </c>
+      <c r="E4" s="12">
+        <f t="shared" si="0"/>
+        <v>812.5</v>
+      </c>
+      <c r="F4" s="22"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="3"/>
+    </row>
+    <row r="5" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="19"/>
+      <c r="C5" s="5">
         <v>20</v>
       </c>
-      <c r="C3" s="4">
-        <v>10000</v>
-      </c>
-      <c r="D3" s="4">
-        <v>13000</v>
-      </c>
-      <c r="E3" s="1">
+      <c r="D5" s="9">
+        <f>D4*C5</f>
+        <v>12500</v>
+      </c>
+      <c r="E5" s="17">
+        <f t="shared" si="0"/>
+        <v>16250</v>
+      </c>
+      <c r="F5" s="5">
         <v>20</v>
       </c>
-      <c r="F3" s="1">
-        <v>6.28</v>
-      </c>
-      <c r="G3" s="1">
-        <f>E3*F3</f>
+      <c r="G5" s="1"/>
+      <c r="H5" s="9">
+        <f>F5*$G$2</f>
         <v>125.60000000000001</v>
       </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="3"/>
-    </row>
-    <row r="4" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="1">
-        <v>36</v>
-      </c>
-      <c r="C4" s="4">
-        <v>8000</v>
-      </c>
-      <c r="D4" s="4">
-        <v>10400</v>
-      </c>
-      <c r="E4" s="1">
-        <v>36</v>
-      </c>
-      <c r="F4" s="1">
-        <v>6.28</v>
-      </c>
-      <c r="G4" s="1">
-        <f t="shared" ref="G4:G11" si="0">E4*F4</f>
-        <v>226.08</v>
-      </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="3"/>
-    </row>
-    <row r="5" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3">
-        <v>700</v>
-      </c>
-      <c r="D5" s="3">
-        <v>910</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H5" s="3"/>
       <c r="I5" s="3"/>
     </row>
     <row r="6" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="1">
-        <v>10</v>
-      </c>
-      <c r="C6" s="4">
-        <v>7000</v>
-      </c>
-      <c r="D6" s="4">
-        <v>9100</v>
-      </c>
-      <c r="E6" s="1">
-        <v>10</v>
-      </c>
-      <c r="F6" s="1">
-        <v>6.28</v>
-      </c>
-      <c r="G6" s="1">
+        <v>52</v>
+      </c>
+      <c r="B6" s="19"/>
+      <c r="C6" s="5">
+        <v>20</v>
+      </c>
+      <c r="D6" s="9">
+        <f>D4*C6</f>
+        <v>12500</v>
+      </c>
+      <c r="E6" s="17">
         <f t="shared" si="0"/>
-        <v>62.800000000000004</v>
-      </c>
-      <c r="H6" s="1"/>
+        <v>16250</v>
+      </c>
+      <c r="F6" s="5">
+        <v>20</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="9">
+        <f>F6*$G$2</f>
+        <v>125.60000000000001</v>
+      </c>
       <c r="I6" s="3"/>
     </row>
     <row r="7" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3">
-        <v>500</v>
-      </c>
-      <c r="D7" s="3">
-        <v>650</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="1">
+      <c r="A7" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="20">
+        <v>180000</v>
+      </c>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12">
+        <f>B7/160</f>
+        <v>1125</v>
+      </c>
+      <c r="E7" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H7" s="3"/>
+        <v>1462.5</v>
+      </c>
+      <c r="F7" s="12"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
       <c r="I7" s="3"/>
     </row>
     <row r="8" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="19"/>
+      <c r="C8" s="6">
         <v>20</v>
       </c>
-      <c r="C8" s="4">
-        <v>20000</v>
-      </c>
-      <c r="D8" s="4">
-        <v>26000</v>
-      </c>
-      <c r="E8" s="1">
+      <c r="D8" s="9">
+        <f>D7*C8</f>
+        <v>22500</v>
+      </c>
+      <c r="E8" s="17">
+        <f t="shared" si="0"/>
+        <v>29250</v>
+      </c>
+      <c r="F8" s="6">
         <v>20</v>
       </c>
-      <c r="F8" s="1">
-        <v>6.28</v>
-      </c>
-      <c r="G8" s="1">
-        <f t="shared" si="0"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="9">
+        <f>F8*$G$2</f>
         <v>125.60000000000001</v>
       </c>
-      <c r="H8" s="1"/>
       <c r="I8" s="3"/>
     </row>
     <row r="9" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="1">
-        <v>24</v>
-      </c>
-      <c r="C9" s="4">
-        <v>12000</v>
-      </c>
-      <c r="D9" s="4">
-        <v>15600</v>
-      </c>
-      <c r="E9" s="1">
-        <v>24</v>
-      </c>
-      <c r="F9" s="1">
-        <v>6.28</v>
-      </c>
-      <c r="G9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="19"/>
+      <c r="C9" s="6">
+        <v>15</v>
+      </c>
+      <c r="D9" s="9">
+        <f>D7*C9</f>
+        <v>16875</v>
+      </c>
+      <c r="E9" s="17">
         <f t="shared" si="0"/>
-        <v>150.72</v>
-      </c>
-      <c r="H9" s="1"/>
+        <v>21937.5</v>
+      </c>
+      <c r="F9" s="6">
+        <v>15</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="9">
+        <f>F9*$G$2</f>
+        <v>94.2</v>
+      </c>
       <c r="I9" s="3"/>
     </row>
     <row r="10" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="1">
-        <v>20</v>
-      </c>
-      <c r="C10" s="4">
-        <v>10000</v>
-      </c>
-      <c r="D10" s="4">
-        <v>13000</v>
-      </c>
-      <c r="E10" s="1">
-        <v>20</v>
-      </c>
-      <c r="F10" s="1">
-        <v>6.28</v>
-      </c>
-      <c r="G10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="19"/>
+      <c r="C10" s="6">
+        <v>15</v>
+      </c>
+      <c r="D10" s="9">
+        <f>D7*C10</f>
+        <v>16875</v>
+      </c>
+      <c r="E10" s="17">
         <f t="shared" si="0"/>
-        <v>125.60000000000001</v>
-      </c>
-      <c r="H10" s="1"/>
+        <v>21937.5</v>
+      </c>
+      <c r="F10" s="6">
+        <v>15</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="9">
+        <f>F10*$G$2</f>
+        <v>94.2</v>
+      </c>
       <c r="I10" s="3"/>
     </row>
     <row r="11" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="7">
-        <v>60</v>
-      </c>
-      <c r="C11" s="4">
-        <v>15000</v>
-      </c>
-      <c r="D11" s="4">
-        <v>19500</v>
-      </c>
-      <c r="E11" s="1">
+      <c r="A11" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="23"/>
+      <c r="C11" s="11">
         <v>30</v>
       </c>
-      <c r="F11" s="1">
-        <v>6.28</v>
-      </c>
-      <c r="G11" s="1">
+      <c r="D11" s="12">
+        <f>D7*C11</f>
+        <v>33750</v>
+      </c>
+      <c r="E11" s="12">
         <f t="shared" si="0"/>
+        <v>43875</v>
+      </c>
+      <c r="F11" s="11">
+        <v>30</v>
+      </c>
+      <c r="G11" s="10"/>
+      <c r="H11" s="9">
+        <f>F11*$G$2</f>
         <v>188.4</v>
       </c>
-      <c r="H11" s="1"/>
       <c r="I11" s="3"/>
     </row>
     <row r="12" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="2">
-        <f>SUM(B2:B11)</f>
-        <v>190</v>
-      </c>
-      <c r="C12" s="5">
-        <v>82000</v>
-      </c>
-      <c r="D12" s="5">
-        <v>106000</v>
-      </c>
-      <c r="E12" s="2">
-        <v>140</v>
-      </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="2">
-        <f>SUM(G3:G11)</f>
-        <v>1004.8000000000001</v>
-      </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="6"/>
+        <v>49</v>
+      </c>
+      <c r="B12" s="15">
+        <v>120000</v>
+      </c>
+      <c r="C12" s="16"/>
+      <c r="D12" s="9">
+        <f>B12/160</f>
+        <v>750</v>
+      </c>
+      <c r="E12" s="17">
+        <f t="shared" si="0"/>
+        <v>975</v>
+      </c>
+      <c r="F12" s="16"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="4"/>
+    </row>
+    <row r="13" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="19"/>
+      <c r="C13" s="7">
+        <v>20</v>
+      </c>
+      <c r="D13" s="9">
+        <f>D12*C13</f>
+        <v>15000</v>
+      </c>
+      <c r="E13" s="17">
+        <f t="shared" si="0"/>
+        <v>19500</v>
+      </c>
+      <c r="F13" s="7">
+        <v>20</v>
+      </c>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+    </row>
+    <row r="14" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="23"/>
+      <c r="C14" s="13">
+        <f>SUM(C13,C8:C11,C5:C6,C3)</f>
+        <v>155</v>
+      </c>
+      <c r="D14" s="14">
+        <f>SUM(D13,D8:D11,D5:D6,D2:D3)</f>
+        <v>150000</v>
+      </c>
+      <c r="E14" s="14">
+        <f>SUM(E13,E11,E8:E11,E5:E6,E3)</f>
+        <v>237250</v>
+      </c>
+      <c r="F14" s="13">
+        <f>SUM(F3:F13)</f>
+        <v>155</v>
+      </c>
+      <c r="G14" s="10"/>
+      <c r="H14" s="24">
+        <f>SUM(H3:H13)</f>
+        <v>847.80000000000007</v>
+      </c>
+      <c r="I14" s="26">
+        <f>SUM(H14,E14,D14)</f>
+        <v>388097.8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="18"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
     </row>
     <row r="16" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>52</v>
-      </c>
+      <c r="A16" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="19"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+    </row>
+    <row r="17" spans="1:8" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="19"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="D3:D4 D12 D7" formula="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -948,39 +1140,39 @@
   <sheetData>
     <row r="1" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -994,7 +1186,7 @@
     </row>
     <row r="3" spans="1:10" ht="27.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B3" s="1">
         <v>0.15</v>
@@ -1009,24 +1201,24 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B4" s="1">
         <v>0.2</v>
@@ -1041,24 +1233,24 @@
         <v>0</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B5" s="1">
         <v>0.05</v>
@@ -1073,24 +1265,24 @@
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -1104,7 +1296,7 @@
     </row>
     <row r="7" spans="1:10" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B7" s="1">
         <v>0.1</v>
@@ -1119,24 +1311,24 @@
         <v>0</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B8" s="1">
         <v>0.05</v>
@@ -1151,24 +1343,24 @@
         <v>0</v>
       </c>
       <c r="F8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -1182,7 +1374,7 @@
     </row>
     <row r="10" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B10" s="1">
         <v>0.05</v>
@@ -1197,24 +1389,24 @@
         <v>0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -1228,10 +1420,10 @@
     </row>
     <row r="12" spans="1:10" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1">
         <v>780</v>
@@ -1243,24 +1435,24 @@
         <v>0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B13" s="2">
         <v>0.60199999999999998</v>
@@ -1273,19 +1465,19 @@
         <v>0</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1312,39 +1504,39 @@
   <sheetData>
     <row r="1" spans="1:10" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1358,7 +1550,7 @@
     </row>
     <row r="3" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B3" s="1">
         <v>0.02</v>
@@ -1370,27 +1562,27 @@
         <v>15.6</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B4" s="1">
         <v>0.03</v>
@@ -1402,27 +1594,27 @@
         <v>23.4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B5" s="1">
         <v>0.01</v>
@@ -1434,27 +1626,27 @@
         <v>7.8</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -1468,7 +1660,7 @@
     </row>
     <row r="7" spans="1:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B7" s="1">
         <v>0.01</v>
@@ -1480,27 +1672,27 @@
         <v>7.8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B8" s="1">
         <v>0.02</v>
@@ -1512,27 +1704,27 @@
         <v>15.6</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -1546,10 +1738,10 @@
     </row>
     <row r="10" spans="1:10" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C10" s="1">
         <v>780</v>
@@ -1558,59 +1750,59 @@
         <v>7.8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B11" s="1">
         <v>0.02</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -1624,10 +1816,10 @@
     </row>
     <row r="13" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C13" s="1">
         <v>780</v>
@@ -1636,27 +1828,27 @@
         <v>6.24</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B14" s="2">
         <v>0.128</v>
@@ -1666,22 +1858,22 @@
         <v>84.24</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
